--- a/Dashboard_GIS/ข้อมูลดิบ/แรงดันน้ำ/PRESSURE_คลองใหญ่_ปีงบ69.xlsx
+++ b/Dashboard_GIS/ข้อมูลดิบ/แรงดันน้ำ/PRESSURE_คลองใหญ่_ปีงบ69.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Report" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="__bookmark_1" vbProcedure="false">Report!$A$4:$M$36</definedName>
+    <definedName function="false" hidden="false" name="__bookmark_1" vbProcedure="false">Report!$A$4:$N$36</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
   <si>
     <t xml:space="preserve">รายงานการตรวจวัดค่าแรงดันน้ำ</t>
   </si>
@@ -322,6 +322,48 @@
         <family val="2"/>
         <charset val="222"/>
       </rPr>
+      <t xml:space="preserve">เม</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">ย</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">. 69</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
       <t xml:space="preserve">ก</t>
     </r>
     <r>
@@ -1142,7 +1184,7 @@
     <t xml:space="preserve">พิมพ์รายงานวันที่</t>
   </si>
   <si>
-    <t xml:space="preserve">5/3/2569</t>
+    <t xml:space="preserve">3/4/2569</t>
   </si>
   <si>
     <t xml:space="preserve">หน้าที่</t>
@@ -1355,7 +1397,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:W41"/>
   <sheetFormatPr defaultColWidth="11.74609375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.6"/>
@@ -1369,15 +1411,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="3.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="23.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="1.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="7.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="1.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="5.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="0.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="2.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="6.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="17.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="1.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="7.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="1.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="5.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="0.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="2.7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1399,11 +1442,12 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="3"/>
+      <c r="Q1" s="2"/>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
@@ -1424,11 +1468,12 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
-      <c r="Q2" s="3"/>
+      <c r="Q2" s="2"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
@@ -1449,11 +1494,12 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
-      <c r="Q3" s="3"/>
+      <c r="Q3" s="2"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
@@ -1469,6 +1515,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
@@ -1503,6 +1550,9 @@
       </c>
       <c r="M5" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1519,13 +1569,14 @@
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -1549,9 +1600,12 @@
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1560,7 +1614,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -1584,9 +1638,12 @@
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1595,7 +1652,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -1619,9 +1676,12 @@
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1630,7 +1690,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -1654,9 +1714,12 @@
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1665,7 +1728,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -1689,9 +1752,12 @@
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1700,7 +1766,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -1724,9 +1790,12 @@
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1735,7 +1804,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -1759,9 +1828,12 @@
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1770,7 +1842,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -1794,9 +1866,12 @@
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1805,7 +1880,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -1829,9 +1904,12 @@
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1840,7 +1918,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -1864,9 +1942,12 @@
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1875,12 +1956,12 @@
         <v>11</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="7" t="n">
-        <v>1.03</v>
+        <v>1.028333</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>1.03</v>
@@ -1899,9 +1980,12 @@
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1910,7 +1994,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -1934,9 +2018,12 @@
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1945,7 +2032,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
@@ -1969,9 +2056,12 @@
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1980,7 +2070,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -2004,9 +2094,12 @@
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2015,7 +2108,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -2039,9 +2132,12 @@
       </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="M21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2050,7 +2146,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -2074,9 +2170,12 @@
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="M22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2085,7 +2184,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -2109,9 +2208,12 @@
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2120,7 +2222,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -2144,9 +2246,12 @@
       </c>
       <c r="K24" s="9"/>
       <c r="L24" s="9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2155,7 +2260,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -2179,9 +2284,12 @@
       </c>
       <c r="K25" s="9"/>
       <c r="L25" s="9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2190,7 +2298,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -2214,9 +2322,12 @@
       </c>
       <c r="K26" s="9"/>
       <c r="L26" s="9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2225,7 +2336,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -2249,9 +2360,12 @@
       </c>
       <c r="K27" s="9"/>
       <c r="L27" s="9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="M27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2260,7 +2374,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -2284,9 +2398,12 @@
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2295,7 +2412,7 @@
         <v>23</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -2319,9 +2436,12 @@
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2330,7 +2450,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -2354,9 +2474,12 @@
       </c>
       <c r="K30" s="9"/>
       <c r="L30" s="9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2365,7 +2488,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -2389,9 +2512,12 @@
       </c>
       <c r="K31" s="9"/>
       <c r="L31" s="9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2400,7 +2526,7 @@
         <v>26</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -2424,9 +2550,12 @@
       </c>
       <c r="K32" s="9"/>
       <c r="L32" s="9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2435,7 +2564,7 @@
         <v>27</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -2459,9 +2588,12 @@
       </c>
       <c r="K33" s="9"/>
       <c r="L33" s="9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2470,7 +2602,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -2494,9 +2626,12 @@
       </c>
       <c r="K34" s="9"/>
       <c r="L34" s="9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2505,7 +2640,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -2529,9 +2664,12 @@
       </c>
       <c r="K35" s="9"/>
       <c r="L35" s="9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2540,7 +2678,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -2564,9 +2702,12 @@
       </c>
       <c r="K36" s="9"/>
       <c r="L36" s="9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2593,10 +2734,11 @@
       <c r="T37" s="10"/>
       <c r="U37" s="10"/>
       <c r="V37" s="10"/>
+      <c r="W37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -2608,7 +2750,7 @@
       <c r="I38" s="11"/>
       <c r="J38" s="11"/>
       <c r="K38" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L38" s="11"/>
       <c r="M38" s="11"/>
@@ -2621,10 +2763,11 @@
       <c r="T38" s="11"/>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
+      <c r="W38" s="11"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -2636,7 +2779,7 @@
       <c r="I39" s="11"/>
       <c r="J39" s="11"/>
       <c r="K39" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L39" s="11"/>
       <c r="M39" s="11"/>
@@ -2649,10 +2792,11 @@
       <c r="T39" s="11"/>
       <c r="U39" s="11"/>
       <c r="V39" s="11"/>
+      <c r="W39" s="11"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -2664,7 +2808,7 @@
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
       <c r="K40" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L40" s="12"/>
       <c r="M40" s="12"/>
@@ -2677,6 +2821,7 @@
       <c r="T40" s="12"/>
       <c r="U40" s="12"/>
       <c r="V40" s="12"/>
+      <c r="W40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13"/>
@@ -2690,39 +2835,40 @@
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
       <c r="K41" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L41" s="13"/>
       <c r="M41" s="13"/>
       <c r="N41" s="13"/>
-      <c r="O41" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="P41" s="13" t="s">
+      <c r="O41" s="13"/>
+      <c r="P41" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="Q41" s="13"/>
-      <c r="R41" s="15" t="s">
+      <c r="Q41" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="S41" s="12" t="s">
+      <c r="R41" s="13"/>
+      <c r="S41" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="T41" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="U41" s="10"/>
+      <c r="T41" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="U41" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="V41" s="10"/>
+      <c r="W41" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="86">
     <mergeCell ref="A1:B3"/>
-    <mergeCell ref="C1:P1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C2:P2"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="C3:P3"/>
-    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="C1:Q1"/>
+    <mergeCell ref="R1:V1"/>
+    <mergeCell ref="C2:Q2"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="C3:Q3"/>
+    <mergeCell ref="R3:V3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="B5:D5"/>
@@ -2790,18 +2936,18 @@
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="A37:J37"/>
-    <mergeCell ref="K37:V37"/>
+    <mergeCell ref="K37:W37"/>
     <mergeCell ref="A38:J38"/>
-    <mergeCell ref="K38:V38"/>
+    <mergeCell ref="K38:W38"/>
     <mergeCell ref="A39:J39"/>
-    <mergeCell ref="K39:V39"/>
+    <mergeCell ref="K39:W39"/>
     <mergeCell ref="A40:J40"/>
-    <mergeCell ref="K40:V40"/>
+    <mergeCell ref="K40:W40"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="D41:J41"/>
-    <mergeCell ref="K41:N41"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="U41:V41"/>
+    <mergeCell ref="K41:O41"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="V41:W41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
